--- a/output/full_scan/batch_gap.xlsx
+++ b/output/full_scan/batch_gap.xlsx
@@ -603,23 +603,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>219</v>
+        <v>66.8</v>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>2158.593048857453</v>
+        <v>1845.054559730246</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -627,7 +627,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>14832235.5</v>
+        <v>4256015.45</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -646,20 +646,20 @@
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>0.2126354020906171</v>
+        <v>1.784465967180936</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.002809253117006893</v>
+        <v>0.9710099442991554</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>214</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="3">
@@ -668,23 +668,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>84.3</v>
+        <v>522</v>
       </c>
       <c r="F3" t="n">
         <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>1726.088903452636</v>
+        <v>1705.278502644527</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -692,7 +692,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>10058769.35</v>
+        <v>13466648.1</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -711,20 +711,20 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>0.4157999519057581</v>
+        <v>1.507308366158111</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.04672645826340126</v>
+        <v>1.288074506798466</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>81.2</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4">
@@ -733,23 +733,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>聯嘉投控</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>24.65</v>
+        <v>39.55</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>1690.356574689148</v>
+        <v>1577.012068917468</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -757,7 +757,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>2583485.25</v>
+        <v>2515294.9</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -776,20 +776,20 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>0.9403351536378279</v>
+        <v>1.721045160037613</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.4719139160358022</v>
+        <v>0.577753668819257</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>24.2</v>
+        <v>37.35</v>
       </c>
     </row>
     <row r="5">
@@ -798,23 +798,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>77.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>1648.945100633161</v>
+        <v>1563.348993775892</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -822,7 +822,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>868697.05</v>
+        <v>134183.05</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -841,45 +841,47 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>0.02376824666990936</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.05787990097984639</v>
-      </c>
+        <v>9.459190492355631</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>gap_chase_after_blowout</t>
+        </is>
+      </c>
       <c r="AI5" t="n">
-        <v>76.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45849</v>
+        <v>46164</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>新光金</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>11.8</v>
+        <v>41.35</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>1607.053623733563</v>
+        <v>1491.913413401012</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -887,7 +889,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>175696015.8</v>
+        <v>1637073.05</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -906,20 +908,20 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
-        <v>-0.2296523829586647</v>
+        <v>-0.03591913377372259</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.02127347373962946</v>
+        <v>0.7985727017362511</v>
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>11.9</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="7">
@@ -928,23 +930,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>79.7</v>
+        <v>118.5</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>1564.48668472553</v>
+        <v>1483.010187514795</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -952,7 +954,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>35135319.15</v>
+        <v>18274549.05</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -971,20 +973,20 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="n">
-        <v>0.1875451244220192</v>
+        <v>1.097097599388108</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1161535949642508</v>
+        <v>0.7041687361434754</v>
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>80</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8">
@@ -993,23 +995,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>381.5</v>
+        <v>26.8</v>
       </c>
       <c r="F8" t="n">
         <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>1454.901929627973</v>
+        <v>1464.577284851702</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -1017,7 +1019,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>1474023.95</v>
+        <v>257918.4</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -1036,20 +1038,20 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="n">
-        <v>0.3532390172636897</v>
+        <v>0.261973030248131</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.322821763545984</v>
+        <v>-0.004149249746754061</v>
       </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>392</v>
+        <v>26.45</v>
       </c>
     </row>
     <row r="9">
@@ -1058,23 +1060,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jpp-KY</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>410</v>
+        <v>130.5</v>
       </c>
       <c r="F9" t="n">
         <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>1453.0526033021</v>
+        <v>1457.493089924878</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -1082,7 +1084,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>2150918.55</v>
+        <v>14321163.7</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1101,20 +1103,24 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="n">
-        <v>0.93371139297695</v>
+        <v>2.234138829546556</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.7670215204989463</v>
+        <v>0.8243348751176759</v>
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>long_upper_shadow, gap_chase_after_blowout</t>
+        </is>
+      </c>
       <c r="AI9" t="n">
-        <v>394</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="10">
@@ -1123,23 +1129,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>氣立</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>49.7</v>
+        <v>53.8</v>
       </c>
       <c r="F10" t="n">
         <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>1408.901566946268</v>
+        <v>1361.066879091209</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -1147,7 +1153,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>792283.15</v>
+        <v>1161164.7</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1166,20 +1172,20 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
-        <v>0.6132903393057298</v>
+        <v>1.302961715878476</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.391379368012073</v>
+        <v>0.2924115545529334</v>
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>46.6</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="11">
@@ -1188,23 +1194,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>炎洲</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>14.05</v>
+        <v>31.4</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>1367.176515914534</v>
+        <v>1299.9433349546</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -1212,7 +1218,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>1282042.15</v>
+        <v>78307.05</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1231,20 +1237,20 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
-        <v>0.2500272545516793</v>
+        <v>0.3049954967980301</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.00934575669212623</v>
+        <v>-0.1570132977919767</v>
       </c>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>13.8</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="12">
@@ -1253,23 +1259,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>拓凱</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>1366.881648590309</v>
+        <v>1267.404556128034</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -1277,7 +1283,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>329603.4</v>
+        <v>4231146.8</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -1296,20 +1302,24 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="n">
-        <v>0.3297262497936277</v>
+        <v>2.30323278610896</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.09659417231995775</v>
+        <v>1.286932462575383</v>
       </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr"/>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>gap_chase_after_blowout</t>
+        </is>
+      </c>
       <c r="AI12" t="n">
-        <v>161</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="13">
@@ -1318,23 +1328,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>特力</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>21.15</v>
+        <v>18.3</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>1362.443237975012</v>
+        <v>1258.570362861448</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -1342,7 +1352,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>261831.4</v>
+        <v>203161.2</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1361,20 +1371,24 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="n">
-        <v>0.1069465699739182</v>
+        <v>0.4958358162893727</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0660035095827412</v>
+        <v>0.605878692649207</v>
       </c>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr"/>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending, stronger_than_market, kd_golden_cross, cci_momentum, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>open_high_close_low</t>
+        </is>
+      </c>
       <c r="AI13" t="n">
-        <v>21.05</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="14">
@@ -1383,23 +1397,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>東台</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>39.45</v>
+        <v>123</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>1353.273795385711</v>
+        <v>1255.219588175546</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -1407,7 +1421,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>10663771.4</v>
+        <v>4907560</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1426,20 +1440,20 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="n">
-        <v>0.5712713094451459</v>
+        <v>4.662184672783178</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.2361512483324567</v>
+        <v>1.124972006133057</v>
       </c>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>40.3</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15">
@@ -1448,23 +1462,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>國精化</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>286.5</v>
+        <v>12.9</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
-        <v>1346.010365656153</v>
+        <v>1242.515592822736</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -1472,7 +1486,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>4806667.45</v>
+        <v>86013.60000000001</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1491,20 +1505,20 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="n">
-        <v>2.508125455676175</v>
+        <v>-0.1911104005114048</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.5098127548533491</v>
+        <v>-0.07797187002064181</v>
       </c>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>264.5</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="16">
@@ -1513,23 +1527,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>810</v>
+        <v>42.85</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>1340.837668434446</v>
+        <v>1240.431995958066</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -1537,7 +1551,7 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>3198408.5</v>
+        <v>288702.9</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -1556,20 +1570,20 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="n">
-        <v>1.715677282119243</v>
+        <v>0.5883379207539805</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.1646530707255169</v>
+        <v>0.3173248853780327</v>
       </c>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
-        <v>826</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="17">
@@ -1578,23 +1592,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>康普</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>101</v>
+        <v>267</v>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>1330.735301739302</v>
+        <v>1232.37882054328</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -1602,7 +1616,7 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>5202556.8</v>
+        <v>1597357.2</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1621,20 +1635,20 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="n">
-        <v>0.7874875145714755</v>
+        <v>2.172830321582925</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.509397629042364</v>
+        <v>1.049793693938981</v>
       </c>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>101.5</v>
+        <v>263.5</v>
       </c>
     </row>
     <row r="18">
@@ -1643,23 +1657,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>麗嬰房</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>8.69</v>
+        <v>227</v>
       </c>
       <c r="F18" t="n">
         <v>11</v>
       </c>
       <c r="G18" t="n">
-        <v>1266.694019495435</v>
+        <v>1225.364397438926</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1667,7 +1681,7 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>402216.75</v>
+        <v>2199301</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1686,22 +1700,20 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="n">
-        <v>1.873594411284814</v>
-      </c>
-      <c r="AE18" t="inlineStr"/>
+        <v>1.774751373463511</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.9361730051071154</v>
+      </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>gap_chase_after_blowout</t>
-        </is>
-      </c>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
-        <v>7.9</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19">
@@ -1710,23 +1722,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>懷特</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>12.9</v>
+        <v>2430</v>
       </c>
       <c r="F19" t="n">
         <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>1263.158343205484</v>
+        <v>1203.719028034811</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1734,7 +1746,7 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>265560.95</v>
+        <v>10591973.3</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1753,20 +1765,24 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="n">
-        <v>-0.1781482666431117</v>
+        <v>1.89577346609478</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.2822278409481197</v>
+        <v>0.5713868521550732</v>
       </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr"/>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>long_upper_shadow</t>
+        </is>
+      </c>
       <c r="AI19" t="n">
-        <v>12.45</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="20">
@@ -1775,23 +1791,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>鈞興-KY</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>229.5</v>
+        <v>56.9</v>
       </c>
       <c r="F20" t="n">
         <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>1251.757890396171</v>
+        <v>1200.25523453446</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1799,7 +1815,7 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>1679562.75</v>
+        <v>4346406.15</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1818,20 +1834,20 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="n">
-        <v>1.54792146492526</v>
+        <v>0.348182549274429</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.3835351443165913</v>
+        <v>0.05833168844880773</v>
       </c>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>232</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="21">
@@ -1840,23 +1856,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>21.7</v>
+        <v>224</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>1240.572073035895</v>
+        <v>1159.502270838033</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1864,7 +1880,7 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>59816906.85</v>
+        <v>15186106.1</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1883,20 +1899,20 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="n">
-        <v>0.1659037723765685</v>
+        <v>3.395861447882788</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.1443639854493231</v>
+        <v>0.2974288377132184</v>
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
-        <v>22.9</v>
+        <v>230.5</v>
       </c>
     </row>
   </sheetData>
